--- a/WorkBot/main/data/order_archive/A.L. George/A.L. George_Triphammer_20260724.xlsx
+++ b/WorkBot/main/data/order_archive/A.L. George/A.L. George_Triphammer_20260724.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E11"/>
+  <dimension ref="A1:E9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -563,48 +563,6 @@
         <v>60</v>
       </c>
     </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>77220</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>Guayaki Yerba Mate - Enlighten Mint</t>
-        </is>
-      </c>
-      <c r="C10" t="n">
-        <v>1</v>
-      </c>
-      <c r="D10" t="n">
-        <v>26</v>
-      </c>
-      <c r="E10" t="n">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>77221</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>Guayaki Yerba Mate - Revel Berry</t>
-        </is>
-      </c>
-      <c r="C11" t="n">
-        <v>1</v>
-      </c>
-      <c r="D11" t="n">
-        <v>26</v>
-      </c>
-      <c r="E11" t="n">
-        <v>26</v>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
